--- a/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-09_notifications_通知_テーブル詳細設計書.xlsx
+++ b/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-09_notifications_通知_テーブル詳細設計書.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>本書の位置づけ：KF-DD-003 は全 9 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち notifications を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
-列・型・NULL・既定値・制約・索引・トリガは backend/schema.sql（KF-DD-003 v2.0 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜022 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
+列・型・NULL・既定値・制約・索引・トリガは backend/src/main/resources/db/migration/V1__init_schema.sql（Flyway。KF-DD-003 v2.2 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜023 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
 章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications）のみ作成している。</t>
         </is>
       </c>
@@ -755,7 +755,7 @@
       <c r="B3" s="7" t="inlineStr">
         <is>
           <t>申請 1〜3 の通知（type・request_id 付き）と付与通知。申請 1 の提出通知（上長宛・未読）、申請 2 の提出通知（上長宛・既読）と承認通知（申請者宛・既読にした例）、申請 3 の提出通知と差戻し通知（申請者宛・未読）、年休付与通知（request_id は NULL）。2 件目の承認通知は INSERT 後に UPDATE で既読化し、updated_at が DB トリガで更新される。
-例の INSERT は schema.sql 実行直後の DB に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
+例の INSERT は V1・V2 適用直後の DB（開発用シードを入れていない状態）に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。</t>
+          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。なお BAT-001〜003 は設計のみで、現行の backend には実装が無い（@Scheduled・pg_dump 呼び出しなし）。</t>
         </is>
       </c>
       <c r="C8" s="9" t="n"/>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>現状は schema.sql（set_updated_at 関数・トリガを含む）の手動実行＋ spring.jpa.hibernate.ddl-auto=validate。列追加・索引追加は ALTER 文を別ファイルにし、将来 Flyway（V1__baseline.sql ＋ V2__… ）へ移行する（KF-DD-003 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+          <t>Flyway（V1__init_schema.sql。set_updated_at 関数・トリガ・初期データを含む）＋ spring.jpa.hibernate.ddl-auto=validate。V1・V2（祝日の初期データ）は適用後に編集せず、列追加・索引追加は次の版 V3__… のように新しいファイルで行う（KF-DD-003・KF-DD-006 参照）。本書 3.4 の提案はこの方式で適用する。</t>
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
@@ -1718,94 +1718,94 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="77.5" customHeight="1">
+    <row r="13" ht="48.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>C-3</t>
+          <t>C-4</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）</t>
+          <t>PK 制約名が未指定で命名規約と不統一</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>先頭の DROP TABLE ... CASCADE（開発用）、DDL、トリガ／関数、初期データ（休暇種別 11 件・部署 3 件）が 1 ファイルに同居している。ヘッダは『PostgreSQL 18／KF-DD-003 v2.0』に修正済みで、旧『H2 / PostgreSQL 共通』の記述は解消。</t>
+          <t>FK は fk_、UNIQUE は uq_、CHECK は ck_ で名前付けされているが、PK だけ無名（PostgreSQL が &lt;表&gt;_pkey を自動付与）。</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>本番 DB で誤実行すると全データを失う。</t>
+          <t>運用上の実害は小さい。制約名での障害解析・ALTER 時に規約と揃わない。</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>schema.sql を DDL 本体（DROP なし）／ dev-reset.sql（DROP）／ seed（初期データ）に分割。将来 Flyway（V1__baseline.sql）へ移行。</t>
+          <t>新規作成時は CONSTRAINT pk_&lt;表&gt; PRIMARY KEY (id) とする（既存は ALTER TABLE ... RENAME CONSTRAINT）。</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="77.5" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>C-5</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>業務ルールの CHECK 制約が少ない</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>コード値の CHECK は主要列にあるが、日付の前後関係・数値の範囲・種別別必須列などは DB で守られずアプリ（Bean Validation／Service）のみで保証している。手動 SQL・バッチ・将来の別入口からは不正データを入れられる。</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>データ不整合の混入余地。各表の個別課題を参照。</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>各表の「推奨 CHECK」を追加（既存データが違反していないことを 10章の確認 SQL で先に確認）。</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
           <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48.5" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>C-4</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>PK 制約名が未指定で命名規約と不統一</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>FK は fk_、UNIQUE は uq_、CHECK は ck_ で名前付けされているが、PK だけ無名（PostgreSQL が &lt;表&gt;_pkey を自動付与）。</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>運用上の実害は小さい。制約名での障害解析・ALTER 時に規約と揃わない。</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>新規作成時は CONSTRAINT pk_&lt;表&gt; PRIMARY KEY (id) とする（既存は ALTER TABLE ... RENAME CONSTRAINT）。</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
         </is>
       </c>
     </row>
     <row r="15" ht="77.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>C-5</t>
+          <t>C-6</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>業務ルールの CHECK 制約が少ない</t>
+          <t>アプリ（Hikari）以外の接続は TimeZone が Asia/Tokyo とは限らない</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>コード値の CHECK は主要列にあるが、日付の前後関係・数値の範囲・種別別必須列などは DB で守られずアプリ（Bean Validation／Service）のみで保証している。手動 SQL・バッチ・将来の別入口からは不正データを入れられる。</t>
+          <t>JST 固定は Hikari の connection-init-sql に依存する（Flyway はアプリの DataSource＝Hikari で実行するため JST）。psql での手動 SQL、BAT-003（設計）の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>データ不整合の混入余地。各表の個別課題を参照。</t>
+          <t>手動 SQL の INSERT／UPDATE で created_at と updated_at トリガの値が 9 時間ずれる。</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>各表の「推奨 CHECK」を追加（既存データが違反していないことを 10章の確認 SQL で先に確認）。</t>
+          <t>ALTER DATABASE kintaiflow SET timezone TO 'Asia/Tokyo'; を併用する（確認 SQL: SHOW timezone;）。</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1814,30 +1814,30 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="63" customHeight="1">
+    <row r="16" ht="92" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>C-6</t>
+          <t>N-2</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>アプリ（Hikari）以外の接続は TimeZone が Asia/Tokyo とは限らない</t>
+          <t>通知の保持・削除方針が無く、取得索引も最適でない</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
+          <t>年 20,000 件増加。ONL-019 は最新 50 件のみ取得し、画面は先頭 5 件。idx_notif_user (user_id, is_read) の is_read を使う SELECT が無く、一覧の ORDER BY created_at DESC, id DESC のソートが残る。月次の重複確認（user_id, type, created_at 範囲）も user_id のみで絞る。</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>手動 SQL の INSERT／UPDATE で created_at と updated_at トリガの値が 9 時間ずれる。</t>
+          <t>数年で行数が増え続ける。1 ユーザーの全通知をソートして上位 50 件を取る無駄が出る。</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>ALTER DATABASE kintaiflow SET timezone TO 'Asia/Tokyo'; を併用する（確認 SQL: SHOW timezone;）。</t>
+          <t>保持 1 年を超える既読通知の削除バッチを追加。索引を (user_id, created_at DESC, id DESC) へ変更。</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1846,30 +1846,30 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="92" customHeight="1">
+    <row r="17" ht="63" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>N-2</t>
+          <t>N-3</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>通知の保持・削除方針が無く、取得索引も最適でない</t>
+          <t>notifications.type の値と request_id の整合を DB が保証しない</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>年 20,000 件増加。ONL-019 は最新 50 件のみ取得し、画面は先頭 5 件。idx_notif_user (user_id, is_read) の is_read を使う SELECT が無く、一覧の ORDER BY created_at DESC, id DESC のソートが残る。月次の重複確認（user_id, type, created_at 範囲）も user_id のみで絞る。</t>
+          <t>type は VARCHAR(30) NULL 可で CHECK が無く、値の妥当性と『REQUEST_* は request_id 必須・LEAVE_* は NULL』は NotificationService#notify の検証のみ。</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>数年で行数が増え続ける。1 ユーザーの全通知をソートして上位 50 件を取る無駄が出る。</t>
+          <t>手動 SQL・バッチで未知の type や request_id 欠落の通知が入る。</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>保持 1 年を超える既読通知の削除バッチを追加。索引を (user_id, created_at DESC, id DESC) へ変更。</t>
+          <t>ck_notif_type / ck_notif_request を追加（type が NULL の旧データは許容）。旧データを整理できれば type を NOT NULL 化。</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1878,30 +1878,30 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="63" customHeight="1">
+    <row r="18" ht="106.5" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>N-3</t>
+          <t>N-4</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>notifications.type の値と request_id の整合を DB が保証しない</t>
+          <t>BAT-002 規格の通知種別・重複判定が ONL-005 / 019 と不一致（要同期）</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>type は VARCHAR(30) NULL 可で CHECK が無く、値の妥当性と『REQUEST_* は request_id 必須・LEAVE_* は NULL』は NotificationService#notify の検証のみ。</t>
+          <t>BAT-002 規格は type="MANDATORY_LEAVE_ALERT"・requestId=null が保存されない前提・message LIKE による重複確認（existsMonthlyByPattern）のままだが、ONL-005 / 019 は NotificationType.LEAVE_ALERT と existsMonthly（user_id, type, 月）を定義。BAT-001 の SQL も type を含まない INSERT のまま。</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>手動 SQL・バッチで未知の type や request_id 欠落の通知が入る。</t>
+          <t>BAT 実装が type を設定しないと type=NULL の通知が作られ、月次重複確認（type 条件）が効かない。</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>ck_notif_type / ck_notif_request を追加（type が NULL の旧データは許容）。旧データを整理できれば type を NOT NULL 化。</t>
+          <t>BAT-001 は LEAVE_GRANTED、BAT-002 は LEAVE_ALERT で notify し、重複確認は existsMonthly に統一するよう BAT 規格を更新する（担当者が更新中）。</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1910,101 +1910,101 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="106.5" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>N-4</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>BAT-002 規格の通知種別・重複判定が ONL-005 / 019 と不一致（要同期）</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>BAT-002 規格は type="MANDATORY_LEAVE_ALERT"・requestId=null が保存されない前提・message LIKE による重複確認（existsMonthlyByPattern）のままだが、ONL-005 / 019 は NotificationType.LEAVE_ALERT と existsMonthly（user_id, type, 月）を定義。BAT-001 の SQL も type を含まない INSERT のまま。</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>BAT 実装が type を設定しないと type=NULL の通知が作られ、月次重複確認（type 条件）が効かない。</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>BAT-001 は LEAVE_GRANTED、BAT-002 は LEAVE_ALERT で notify し、重複確認は existsMonthly に統一するよう BAT 規格を更新する（担当者が更新中）。</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>9.2b 解消済み（v2.0）の課題（履歴。この版で対応済み）</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>解消内容</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>根拠（DDL／規格）</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>残る事項</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="106.5" customHeight="1">
+    <row r="22" ht="106.5" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>C-1</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>updated_at が更新時に自動更新されない</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="135.5" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>C-1</t>
+          <t>C-2</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>updated_at が更新時に自動更新されない</t>
+          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
+          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。業務時刻は Clock（ClockConfig / AppTime。Asia/Tokyo 固定）から取得した LocalDateTime をそのまま保存する。hibernate.jdbc.time_zone は設定していない（application.properties に無い）。Docker では ENV TZ=Asia/Tokyo。</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
+          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -2018,25 +2018,25 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="92" customHeight="1">
+    <row r="24" ht="135.5" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>C-2</t>
+          <t>C-3</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
+          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）／手動実行</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
+          <t>schema.sql を廃止し Flyway（backend/src/main/resources/db/migration/V1__init_schema.sql）へ移行。V1 は DROP を含まず、DDL・トリガ・初期データ（休暇種別 11 件・部署 5 件）を持つ。ユーザーは V1 に含めずアプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る。開発用の全消去は backend/db/reset-dev.sql に分離。V1 は編集せず、変更は V2 以降を追加する。ddl-auto=validate を継続。</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
+          <t>旧 schema.sql 由来の開発 DB は baseline-on-migrate で V1 適用済みとみなされ、V1 の追加列（users の 4 列）が入らない。reset-dev.sql で作り直す必要がある。</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -2230,7 +2230,7 @@
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="C28:F28"/>
   </mergeCells>
@@ -2557,10 +2557,10 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="10" t="n"/>
     </row>
-    <row r="15" ht="19.5" customHeight="1">
+    <row r="15" ht="34" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>全 SQL を PostgreSQL 16 上で schema.sql（v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
+          <t>全 SQL を PostgreSQL 16 上で V1__init_schema.sql（v2.0・トリガ含む）＋ V2__seed_holidays.sql ＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
         </is>
       </c>
       <c r="B15" s="9" t="n"/>
@@ -2598,7 +2598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2657,6 +2657,29 @@
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>V2 追加に伴いデータ例の前提を更新。保存期間（既読 1 年経過で削除）の自動削除は未実装であることを課題 C-7 として追加。</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2734,7 +2757,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>PostgreSQL 18 / UTF-8。DDL の正は backend/schema.sql。</t>
+          <t>PostgreSQL 18 / UTF-8。DDL の正は Flyway の V1__init_schema.sql（backend/src/main/resources/db/migration）。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -3374,10 +3397,10 @@
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="10" t="n"/>
     </row>
-    <row r="38" ht="19.5" customHeight="1">
+    <row r="38" ht="63" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>backend/schema.sql</t>
+          <t>backend/src/main/resources/db/migration/V1__init_schema.sql</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -3465,7 +3488,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>2.1 列定義（schema.sql から自動生成）</t>
+          <t>2.1 列定義（V1__init_schema.sql から自動生成）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -4026,7 +4049,7 @@
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
+          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は V1__init_schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
         </is>
       </c>
       <c r="B12" s="9" t="n"/>
@@ -4073,7 +4096,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>3.1 制約一覧（schema.sql の定義名のまま）</t>
+          <t>3.1 制約一覧（V1__init_schema.sql の定義名のまま）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -4355,7 +4378,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="164.5" customHeight="1">
+    <row r="14" ht="222.5" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
           <t>idx_notif_user</t>
@@ -4373,7 +4396,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>CREATE INDEX（schema.sql）</t>
+          <t>CREATE INDEX（V1__init_schema.sql）</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -4387,6 +4410,7 @@
 ○ ONL-019 所有確認つきの通知検索  [先頭 1/2 列で絞込]  WHERE id = ? AND user_id = ?
 ○ ONL-019 既読化  [先頭 2/2 列で絞込]  WHERE id = ? AND user_id = ? AND is_read = FALSE
 ○ ONL-019 月次の重複確認  [先頭 1/2 列で絞込]  WHERE user_id = ? AND type = ? AND created_at &gt;= ? AND created_at &lt; ?
+○ ONL-019 本文キー付き月次の重複確認  [先頭 1/2 列で絞込]  WHERE user_id = ? AND type = ? AND message LIKE ? ESCAPE '\' AND created_at &gt;= ? AND created_at 
 ○ BAT-002 ⑤ 同月重複の確認（ONL-019 existsMonthly。BA</t>
         </is>
       </c>
@@ -4470,7 +4494,7 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>3.4 推奨する変更（schema.sql は変更しない。提案のみ。DDL は schema.sql＋8章データに対して実行確認済み）</t>
+          <t>3.4 推奨する変更（V1__init_schema.sql は変更しない。提案のみ。DDL は V1・V2＋8章データに対して実行確認済み）</t>
         </is>
       </c>
       <c r="B22" s="9" t="n"/>
@@ -5252,7 +5276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:J33"/>
+  <dimension ref="A2:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6198,115 +6222,126 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="48.5" customHeight="1">
+    <row r="29" ht="106.5" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
+          <t>ONL-019</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>通知一覧取得</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>本文キー付き月次の重複確認（NotificationRepository#existsByUserIdAndTypeAndMessageStartingWithAndCreatedAtGreaterThanEqualAndCreatedAtLessThan。4 引数 overload）</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>SELECT 1 FROM notifications
+ WHERE user_id = ? AND type = ? AND message LIKE ? ESCAPE '\'
+   AND created_at &gt;= ? AND created_at &lt; ?
+ LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>user_id = ? AND type = ? AND message LIKE ? ESCAPE '\' AND created_at &gt;= ? AND created_at &lt; ?</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>1ユーザー分（LIMIT 50 あり）</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>○idx_notif_user</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48.5" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
           <t>ONL-022</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>申請提出</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>通知の登録（NotificationService#notify）</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>INSERT INTO notifications (user_id, type, request_id, message, is_read)
   VALUES (?, 'REQUEST_SUBMITTED', ?, ?, FALSE)</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr"/>
-      <c r="G29" s="12" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr"/>
+      <c r="G30" s="12" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>1 件</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>（索引なし／PK 結合）</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>BAT-001</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>年次有給休暇 自動付与</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>⑥ 通知の登録（notify）</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>INSERT INTO notifications (user_id, type, request_id, message) VALUES (?, 'LEAVE_GRANTED', NULL, ?)</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>（バッチ 1 回あたり：対象者数に比例）</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31" ht="63" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>BAT-002</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>年5日取得義務アラート</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>⑤ 同月重複の確認（ONL-019 existsMonthly。BAT-002 規格は message LIKE のまま＝課題 N-4）</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>SELECT 1 FROM notifications WHERE user_id = ? AND type = 'LEAVE_ALERT' AND created_at &gt;= ? AND created_at &lt; ? LIMIT 1</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
@@ -6318,12 +6353,12 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>なし（READ COMMITTED）</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr"/>
     </row>
-    <row r="32" ht="34" customHeight="1">
+    <row r="32" ht="63" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
           <t>BAT-002</t>
@@ -6336,17 +6371,17 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>⑥ 通知の登録（notify）</t>
+          <t>⑤ 同月重複の確認（ONL-019 existsMonthly。BAT-002 規格は message LIKE のまま＝課題 N-4）</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO notifications (user_id, type, request_id, message) VALUES (?, 'LEAVE_ALERT', NULL, ?)</t>
+          <t>SELECT 1 FROM notifications WHERE user_id = ? AND type = 'LEAVE_ALERT' AND created_at &gt;= ? AND created_at &lt; ? LIMIT 1</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
@@ -6358,26 +6393,66 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>BAT-002</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>年5日取得義務アラート</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>⑥ 通知の登録（notify）</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO notifications (user_id, type, request_id, message) VALUES (?, 'LEAVE_ALERT', NULL, ?)</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>（バッチ 1 回あたり：対象者数に比例）</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>※ 想定件数・使用索引はクエリ条件から機械的に推定した目安。Hibernate が発行する SQL は列を全て列挙する（SELECT * と表記）。BAT-003 は pg_dump（COPY）による全件読取のためこの表では省略。</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="10" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -6391,11 +6466,11 @@
     <mergeCell ref="D8:J8"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A34:J34"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="D11:J11"/>
     <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A33:J33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
